--- a/data/employees/EMP096/AST-EMP096-06.xlsx
+++ b/data/employees/EMP096/AST-EMP096-06.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project Resource Tracker" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,36 +26,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="002E4057"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00048A81"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -69,17 +47,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,210 +414,1883 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Project Resource Tracker - Avery Wilson (Engineering)</t>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>EmployeeId</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Narrative</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Author: Avery Wilson | Role: Engineer | Location: Hsinchu | Date: 2025-04-19</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-W01</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>73</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-W02</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>87</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Project</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Milestone</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Planned</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Actual</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Resources</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-W03</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>69</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Proj Alpha</t>
+          <t>EMP096</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp096 06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W04</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-02-01</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2025-01-29</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>70</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>4</v>
+          <t>Section 1: Automation backlog refinement. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Proj Beta</t>
+          <t>EMP096</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M2 - Build</t>
+          <t>Ast Emp096 06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Team B</t>
+          <t>2026-W05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2025-03-20</t>
-        </is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Delayed</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
+          <t>Section 1: Fabric semantic model planning. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Proj Gamma</t>
+          <t>EMP096</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M1 - Design</t>
+          <t>Ast Emp096 06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Team C</t>
+          <t>2026-W06</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2025-04-01</t>
-        </is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>69</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>On Track</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>3</v>
+          <t>Section 1: Fabric semantic model planning. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Proj Delta</t>
+          <t>EMP096</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M3 - Test</t>
+          <t>Ast Emp096 06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Team A</t>
+          <t>2026-W07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
-        </is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>79</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>At Risk</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>5</v>
+          <t>Section 1: Department KPI performance. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-W08</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>83</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-W09</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-W10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Quality</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>71</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>83</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Innovation</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>66</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>75</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>71</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>71</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>70</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>87</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>94</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-W19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>93</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-W20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>63</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-W21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>84</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-W22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>82</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-W23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>63</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ast Emp096 06</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-W24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Mentoring</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>85</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2026-01-04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-01-10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-01-13</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-01-25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-08</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Section 1: Department KPI performance. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Section 1: Operational risk review. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Data quality remediation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Knowledge transfer and onboarding</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Section 1: Quarterly delivery milestones. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Customer escalation analysis</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Department KPI performance</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Section 1: Knowledge transfer and onboarding. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Fabric semantic model planning</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Section 1: Data quality remediation. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Automation backlog refinement</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Section 1: Customer escalation analysis. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Operational risk review</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Section 1: Fabric semantic model planning. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Quarterly delivery milestones</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>EMP096</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Section 1: Automation backlog refinement. EMP096 contributes to ast emp096 06 through recurring collaboration, clear ownership boundaries, and measurable outcomes. The team captures decisions, open issues, and handoffs so that knowledge remains discoverable for future programs.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>